--- a/Result/profitability/5468.xlsx
+++ b/Result/profitability/5468.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.11625</v>
+        <v>-0.10375</v>
       </c>
       <c r="N2" t="n">
-        <v>29.4425</v>
+        <v>30.4125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1375</v>
+        <v>-0.13875</v>
       </c>
       <c r="N3" t="n">
-        <v>29.9175</v>
+        <v>30.24375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.18625</v>
+        <v>-0.1875</v>
       </c>
       <c r="N4" t="n">
-        <v>28.38125</v>
+        <v>29.1025</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2325</v>
+        <v>-0.2075</v>
       </c>
       <c r="N5" t="n">
-        <v>28.905</v>
+        <v>30.42875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.28</v>
+        <v>-0.2675</v>
       </c>
       <c r="N6" t="n">
-        <v>24.495</v>
+        <v>26.215</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.30125</v>
+        <v>-0.24375</v>
       </c>
       <c r="N7" t="n">
-        <v>25.1475</v>
+        <v>25.38375</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2787500000000001</v>
+        <v>-0.29125</v>
       </c>
       <c r="N8" t="n">
-        <v>26.7875</v>
+        <v>26.86875</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5468</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>35</v>
+      </c>
+      <c r="D75" t="n">
+        <v>23</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07250000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.51125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6500000000000057</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01834085778781058</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.111111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5100418410041843</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
